--- a/src/CA_train.xlsx
+++ b/src/CA_train.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B620"/>
+  <dimension ref="A1:B450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,5590 +1043,3890 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A32V</t>
+          <t>I33A</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1.083296411</v>
+        <v>1.167478954</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A32I</t>
+          <t>I33I</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.697828977</v>
+        <v>1.034559149</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A32L</t>
+          <t>G34A</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.635799734</v>
+        <v>0.974410134</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A32M</t>
+          <t>G34G</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.78201152</v>
+        <v>1.078347215</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A32F</t>
+          <t>K35A</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.595923793</v>
+        <v>1.104331485</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A32Y</t>
+          <t>K35K</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.702259637</v>
+        <v>0.840776744</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A32W</t>
+          <t>N36A</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.910500665</v>
+        <v>1.004106443</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A32H</t>
+          <t>N36N</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.808595481</v>
+        <v>0.98554625</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A32K</t>
+          <t>Q37A</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1.05671245</v>
+        <v>0.126209313</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A32R</t>
+          <t>Q37Q</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1.154186974</v>
+        <v>0.887177227</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A32D</t>
+          <t>S38A</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1.114311032</v>
+        <v>0.970698095</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A32E</t>
+          <t>S38S</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1.149756314</v>
+        <v>0.937289748</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A32N</t>
+          <t>P39A</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1.087727071</v>
+        <v>0.191169988</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A32Q</t>
+          <t>P39P</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1.04785113</v>
+        <v>0.9038813999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A32S</t>
+          <t>I40A</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1.140894993</v>
+        <v>0.881609169</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A32T</t>
+          <t>I40I</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1.158617634</v>
+        <v>0.8667610140000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A32C</t>
+          <t>D41A</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.78201152</v>
+        <v>0.7980883</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A32G</t>
+          <t>D41D</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1.127603013</v>
+        <v>0.95770596</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A32P</t>
+          <t>L42A</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.52060257</v>
+        <v>0.842632763</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>I33A</t>
+          <t>L42L</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1.167478954</v>
+        <v>1.017098578</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>I33I</t>
+          <t>N43A</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.034559149</v>
+        <v>1.015242559</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>G34A</t>
+          <t>N43N</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.974410134</v>
+        <v>0.907593439</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>G34G</t>
+          <t>E44A</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.078347215</v>
+        <v>1.083915273</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>K35A</t>
+          <t>E44E</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1.104331485</v>
+        <v>0.93172169</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>K35K</t>
+          <t>K45A</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.840776744</v>
+        <v>0.970698095</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>N36A</t>
+          <t>K45K</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.004106443</v>
+        <v>0.870473053</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>N36N</t>
+          <t>Y46A</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.98554625</v>
+        <v>1.03751479</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Q37A</t>
+          <t>Y46Y</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.126209313</v>
+        <v>1.204556527</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Q37Q</t>
+          <t>M47A</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.887177227</v>
+        <v>1.299213512</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>S38A</t>
+          <t>M47M</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.970698095</v>
+        <v>1.005962462</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>S38S</t>
+          <t>V48A</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.937289748</v>
+        <v>1.265805164</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>P39A</t>
+          <t>V48V</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.191169988</v>
+        <v>1.262093126</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>P39P</t>
+          <t>K49A</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.9038813999999999</v>
+        <v>1.347470014</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>I40A</t>
+          <t>K49K</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.881609169</v>
+        <v>1.343015567</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>I40I</t>
+          <t>A50A</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.8667610140000001</v>
+        <v>1.303759934</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>D41A</t>
+          <t>C51A</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7980883</v>
+        <v>1.520104377</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>D41D</t>
+          <t>C51C</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.95770596</v>
+        <v>1.163325821</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>L42A</t>
+          <t>T52A</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.842632763</v>
+        <v>1.19748547</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>L42L</t>
+          <t>T52T</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.017098578</v>
+        <v>1.167121338</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>N43A</t>
+          <t>R53A</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1.015242559</v>
+        <v>1.077926699</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>N43N</t>
+          <t>R53R</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.907593439</v>
+        <v>1.024789467</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>E44A</t>
+          <t>P54A</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1.083915273</v>
+        <v>1.038073775</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>E44E</t>
+          <t>P54P</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.93172169</v>
+        <v>0.9811410270000001</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>K45A</t>
+          <t>L55A</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.970698095</v>
+        <v>1.248724944</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>K45K</t>
+          <t>L55L</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.870473053</v>
+        <v>0.9716522359999999</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Y46A</t>
+          <t>Q56A</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1.03751479</v>
+        <v>0.994425335</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Y46Y</t>
+          <t>Q56Q</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1.204556527</v>
+        <v>1.028584984</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>M47A</t>
+          <t>I57A</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1.299213512</v>
+        <v>1.020993951</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>M47M</t>
+          <t>I57I</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1.005962462</v>
+        <v>0.975447752</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>V48A</t>
+          <t>N58A</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.265805164</v>
+        <v>1.007709643</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>V48V</t>
+          <t>N58N</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1.262093126</v>
+        <v>1.113984106</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>K49A</t>
+          <t>Y59A</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1.347470014</v>
+        <v>1.129166172</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>K49K</t>
+          <t>Y59Y</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1.343015567</v>
+        <v>1.064642391</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A50A</t>
+          <t>V60A</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1.303759934</v>
+        <v>1.070335666</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A50V</t>
+          <t>V60V</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1.531490926</v>
+        <v>0.998220852</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A50I</t>
+          <t>A61A</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1.383465781</v>
+        <v>1.15383703</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A50L</t>
+          <t>D62A</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.349306132</v>
+        <v>1.01150516</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A50M</t>
+          <t>D62D</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1.360692682</v>
+        <v>1.09880204</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A50F</t>
+          <t>A63A</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1.125370656</v>
+        <v>1.195587712</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A50Y</t>
+          <t>V64A</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1.375874748</v>
+        <v>1.334124066</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A50W</t>
+          <t>V64V</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1.364488198</v>
+        <v>1.20887202</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A50H</t>
+          <t>K65A</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1.322737516</v>
+        <v>1.391056814</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A50K</t>
+          <t>K65K</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1.394852331</v>
+        <v>1.288577867</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A50R</t>
+          <t>V66A</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1.42901198</v>
+        <v>1.272516786</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A50D</t>
+          <t>V66V</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1.322737516</v>
+        <v>1.435517481</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A50E</t>
+          <t>L67A</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1.216463053</v>
+        <v>1.159527668</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A50N</t>
+          <t>L67L</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1.334124066</v>
+        <v>0.870571892</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A50Q</t>
+          <t>N68A</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1.284782351</v>
+        <v>0.968742765</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A50S</t>
+          <t>N68N</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1.125370656</v>
+        <v>0.961333642</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A50T</t>
+          <t>N69A</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1.326533033</v>
+        <v>0.889094698</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A50C</t>
+          <t>N69N</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1.318942</v>
+        <v>0.959481361</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A50G</t>
+          <t>G70A</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1.364488198</v>
+        <v>0.879833295</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A50P</t>
+          <t>G70G</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1.144348239</v>
+        <v>0.9539245200000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>C51A</t>
+          <t>H71A</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1.520104377</v>
+        <v>0.92428803</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>C51C</t>
+          <t>H71H</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1.163325821</v>
+        <v>0.931697152</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>T52A</t>
+          <t>T72A</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1.19748547</v>
+        <v>0.726094003</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>T52T</t>
+          <t>T72T</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1.167121338</v>
+        <v>0.863162769</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>R53A</t>
+          <t>I73A</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1.077926699</v>
+        <v>0.911322065</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>R53R</t>
+          <t>I73I</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1.024789467</v>
+        <v>0.959481361</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>P54A</t>
+          <t>K74A</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1.038073775</v>
+        <v>0.581616115</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>P54P</t>
+          <t>K74K</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.9811410270000001</v>
+        <v>0.9631859230000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>L55A</t>
+          <t>V75A</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1.248724944</v>
+        <v>0.979856448</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>L55L</t>
+          <t>V75V</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.9716522359999999</v>
+        <v>1.046538551</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Q56A</t>
+          <t>I76A</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.994425335</v>
+        <v>1.022458903</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Q56Q</t>
+          <t>I76I</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>1.028584984</v>
+        <v>0.907617504</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>I57A</t>
+          <t>T77A</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1.020993951</v>
+        <v>1.046538551</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>I57I</t>
+          <t>T77T</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.975447752</v>
+        <v>0.89465154</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>N58A</t>
+          <t>L78A</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1.007709643</v>
+        <v>1.174345913</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>N58N</t>
+          <t>L78L</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1.113984106</v>
+        <v>0.948367678</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Y59A</t>
+          <t>G79A</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1.129166172</v>
+        <v>1.057652234</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Y59Y</t>
+          <t>G79G</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>1.064642391</v>
+        <v>1.065061357</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>V60A</t>
+          <t>K80A</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>1.070335666</v>
+        <v>0.998379254</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>V60V</t>
+          <t>K80K</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.998220852</v>
+        <v>0.965038203</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A61A</t>
+          <t>S81A</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1.15383703</v>
+        <v>1.203982403</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A61V</t>
+          <t>S81S</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1.070335666</v>
+        <v>1.274369067</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A61I</t>
+          <t>Y82A</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>1.036176017</v>
+        <v>1.070337707</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A61L</t>
+          <t>Y82Y</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.9071284549999999</v>
+        <v>1.276833728</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A61M</t>
+          <t>V83A</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.95647017</v>
+        <v>0.958485696</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A61F</t>
+          <t>V83V</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.827422607</v>
+        <v>1.006668101</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A61Y</t>
+          <t>V84A</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1.002016368</v>
+        <v>0.111852011</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A61W</t>
+          <t>V84V</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.948879137</v>
+        <v>1.130565713</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A61H</t>
+          <t>I85A</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.94508362</v>
+        <v>1.092708109</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A61K</t>
+          <t>I85I</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.6983750439999999</v>
+        <v>0.968810497</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A61R</t>
+          <t>D86A</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.827422607</v>
+        <v>0.906861691</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A61D</t>
+          <t>D86D</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1.146245997</v>
+        <v>0.948160895</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A61E</t>
+          <t>G87A</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1.077926699</v>
+        <v>0.9653688969999999</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A61N</t>
+          <t>G87G</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1.161428063</v>
+        <v>0.9653688969999999</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A61Q</t>
+          <t>R88A</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>1.161428063</v>
+        <v>0.9412776940000001</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A61S</t>
+          <t>R88R</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.967856719</v>
+        <v>0.89653689</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A61T</t>
+          <t>K89A</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>1.020993951</v>
+        <v>0.920628092</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A61C</t>
+          <t>K89K</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>1.04376705</v>
+        <v>0.879328888</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A61G</t>
+          <t>F90A</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1.005811885</v>
+        <v>0.825984083</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A61P</t>
+          <t>F90F</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>0.880559839</v>
+        <v>0.836308884</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>D62A</t>
+          <t>Y91A</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>1.01150516</v>
+        <v>0.987739299</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>D62D</t>
+          <t>Y91Y</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>1.09880204</v>
+        <v>0.8810496880000001</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A63A</t>
+          <t>L92A</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>1.195587712</v>
+        <v>0.853516885</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A63V</t>
+          <t>L92L</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1.032380501</v>
+        <v>0.863841686</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A63I</t>
+          <t>R93A</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.891946388</v>
+        <v>1.037642504</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A63L</t>
+          <t>R93R</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.872968806</v>
+        <v>1.089266509</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A63M</t>
+          <t>Q94A</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.983038785</v>
+        <v>0.366530437</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A63F</t>
+          <t>Q94Q</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.671806429</v>
+        <v>0.9412776940000001</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A63Y</t>
+          <t>F95A</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.880559839</v>
+        <v>0.922348892</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A63W</t>
+          <t>F95F</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.759103309</v>
+        <v>1.008388901</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A63H</t>
+          <t>H96A</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>0.918515004</v>
+        <v>0.657345666</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A63K</t>
+          <t>H96H</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.903332938</v>
+        <v>0.918907292</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A63R</t>
+          <t>F97A</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1.085517732</v>
+        <v>1.326736933</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A63D</t>
+          <t>F97F</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>1.157632547</v>
+        <v>1.388685739</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A63E</t>
+          <t>H98A</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>1.081722216</v>
+        <v>-0.220549056</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A63N</t>
+          <t>H98H</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>1.108290831</v>
+        <v>0.86922275</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A63Q</t>
+          <t>A99A</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>1.123472898</v>
+        <v>1.275107147</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A63S</t>
+          <t>P100A</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>1.150041513</v>
+        <v>1.325147689</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A63T</t>
+          <t>P100P</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.998220852</v>
+        <v>1.061971505</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A63C</t>
+          <t>S101A</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.937492587</v>
+        <v>1.477122669</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A63G</t>
+          <t>S101S</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1.066540149</v>
+        <v>0.980423955</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A63P</t>
+          <t>E102A</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1.051358083</v>
+        <v>0.129734739</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>V64A</t>
+          <t>E102E</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>1.334124066</v>
+        <v>0.978570601</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>V64V</t>
+          <t>H103A</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>1.20887202</v>
+        <v>0.698714236</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>K65A</t>
+          <t>H103H</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>1.391056814</v>
+        <v>0.872929457</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>K65K</t>
+          <t>T104A</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>1.288577867</v>
+        <v>1.212093131</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>V66A</t>
+          <t>T104T</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>1.272516786</v>
+        <v>0.930383412</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>V66V</t>
+          <t>V105A</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>1.435517481</v>
+        <v>0.969303834</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>L67A</t>
+          <t>V105V</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>1.159527668</v>
+        <v>0.935943473</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>L67L</t>
+          <t>N106A</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.870571892</v>
+        <v>1.132398934</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>N68A</t>
+          <t>N106N</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.968742765</v>
+        <v>0.9952507819999999</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>N68N</t>
+          <t>G107A</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.961333642</v>
+        <v>1.143519055</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>N69A</t>
+          <t>G107G</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.889094698</v>
+        <v>0.9952507819999999</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>N69N</t>
+          <t>E108A</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.959481361</v>
+        <v>1.349241283</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>G70A</t>
+          <t>E108E</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.879833295</v>
+        <v>1.011930963</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>G70G</t>
+          <t>Y109A</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.9539245200000001</v>
+        <v>1.11942546</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>H71A</t>
+          <t>Y109Y</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.92428803</v>
+        <v>0.985984015</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>H71H</t>
+          <t>Y110A</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.931697152</v>
+        <v>1.345534577</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>T72A</t>
+          <t>Y110Y</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.726094003</v>
+        <v>1.030464497</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>T72T</t>
+          <t>P111A</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.863162769</v>
+        <v>1.000810842</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>I73A</t>
+          <t>P111P</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.911322065</v>
+        <v>0.7376346580000001</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>I73I</t>
+          <t>F112A</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.959481361</v>
+        <v>1.477122669</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>K74A</t>
+          <t>F112F</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.581616115</v>
+        <v>1.017491023</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>K74K</t>
+          <t>E113A</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.9631859230000001</v>
+        <v>1.321440982</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>V75A</t>
+          <t>E113E</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.979856448</v>
+        <v>1.321440982</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>V75V</t>
+          <t>A114A</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1.046538551</v>
+        <v>0.364431364</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>I76A</t>
+          <t>H115A</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>1.022458903</v>
+        <v>0.9170667179999999</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>I76I</t>
+          <t>H115H</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>0.907617504</v>
+        <v>0.889691592</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>T77A</t>
+          <t>F116A</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>1.046538551</v>
+        <v>0.653581131</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>T77T</t>
+          <t>F116F</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.89465154</v>
+        <v>0.198469663</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>L78A</t>
+          <t>V117A</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1.174345913</v>
+        <v>1.31913888</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>L78L</t>
+          <t>V117V</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.948367678</v>
+        <v>1.384154804</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>G79A</t>
+          <t>H118A</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1.057652234</v>
+        <v>-0.219286</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>G79G</t>
+          <t>H118H</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>1.065061357</v>
+        <v>0.864244822</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>K80A</t>
+          <t>T119A</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>0.998379254</v>
+        <v>1.267804771</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>K80K</t>
+          <t>T119T</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>0.965038203</v>
+        <v>0.785007024</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>S81A</t>
+          <t>D120A</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>1.203982403</v>
+        <v>1.317558738</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S81S</t>
+          <t>D120D</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>1.274369067</v>
+        <v>0.027641092</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Y82A</t>
+          <t>D121A</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1.070337707</v>
+        <v>1.468663376</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Y82Y</t>
+          <t>D121D</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1.276833728</v>
+        <v>0.724196621</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>V83A</t>
+          <t>E122A</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.958485696</v>
+        <v>0.128991765</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>V83V</t>
+          <t>E122E</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>1.006668101</v>
+        <v>0.972966452</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>V84A</t>
+          <t>G123A</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.111852011</v>
+        <v>0.694712789</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>V84V</t>
+          <t>G123G</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>1.130565713</v>
+        <v>0.698398268</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>I85A</t>
+          <t>N124A</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>1.092708109</v>
+        <v>1.205151628</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>I85I</t>
+          <t>N124N</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.968810497</v>
+        <v>1.05404699</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>D86A</t>
+          <t>I125A</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.906861691</v>
+        <v>0.963752755</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>D86D</t>
+          <t>I125I</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.948160895</v>
+        <v>1.015349461</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>G87A</t>
+          <t>A126A</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.9653688969999999</v>
+        <v>1.12591383</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>G87G</t>
+          <t>V127A</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>0.9653688969999999</v>
+        <v>1.136970267</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>R88A</t>
+          <t>V127V</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.9412776940000001</v>
+        <v>0.937954402</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>R88R</t>
+          <t>I128A</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.89653689</v>
+        <v>1.341514351</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>K89A</t>
+          <t>I128I</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.920628092</v>
+        <v>1.035619595</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>K89K</t>
+          <t>G129A</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.879328888</v>
+        <v>1.113014654</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>F90A</t>
+          <t>G129G</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.825984083</v>
+        <v>1.05404699</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>F90F</t>
+          <t>V130A</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.836308884</v>
+        <v>1.421851466</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Y91A</t>
+          <t>V130V</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.987739299</v>
+        <v>1.299501796</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Y91Y</t>
+          <t>L131A</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.8810496880000001</v>
+        <v>1.421851466</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>L92A</t>
+          <t>L131L</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>0.853516885</v>
+        <v>0.954698181</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>L92L</t>
+          <t>F132A</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.863841686</v>
+        <v>1.305063144</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>R93A</t>
+          <t>F132F</t>
         </is>
       </c>
       <c r="B255" t="n">
-        <v>1.037642504</v>
+        <v>0.874985517</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>R93R</t>
+          <t>K133A</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>1.089266509</v>
+        <v>1.277256401</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Q94A</t>
+          <t>K133K</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.366530437</v>
+        <v>0.97323601</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Q94Q</t>
+          <t>L134A</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.9412776940000001</v>
+        <v>1.156760514</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>F95A</t>
+          <t>L134L</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>0.922348892</v>
+        <v>0.956551964</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>F95F</t>
+          <t>G135A</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>1.008388901</v>
+        <v>1.253157224</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>H96A</t>
+          <t>G135G</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.657345666</v>
+        <v>1.067778936</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>H96H</t>
+          <t>K136A</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.918907292</v>
+        <v>1.106708377</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>F97A</t>
+          <t>K136K</t>
         </is>
       </c>
       <c r="B263" t="n">
-        <v>1.326736933</v>
+        <v>0.925037655</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>F97F</t>
+          <t>T137A</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>1.388685739</v>
+        <v>1.077047851</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>H98A</t>
+          <t>T137T</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>-0.220549056</v>
+        <v>1.006604101</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>H98H</t>
+          <t>N138A</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>0.86922275</v>
+        <v>1.101147028</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>A99A</t>
+          <t>N138N</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>1.275107147</v>
+        <v>1.101147028</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>A99V</t>
+          <t>K139A</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>1.156492529</v>
+        <v>1.245742092</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>A99I</t>
+          <t>K139K</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>-0.144561566</v>
+        <v>0.978797358</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>A99L</t>
+          <t>E140A</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.8859029309999999</v>
+        <v>0.90279226</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>A99M</t>
+          <t>E140E</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.7635816050000001</v>
+        <v>1.032557062</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>A99F</t>
+          <t>L141A</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.707981003</v>
+        <v>1.021434365</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>A99Y</t>
+          <t>L141L</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>1.112012047</v>
+        <v>0.869424169</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>A99W</t>
+          <t>Q142A</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.86366269</v>
+        <v>1.208666435</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>A99H</t>
+          <t>Q142Q</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>-0.06301401600000001</v>
+        <v>1.056656239</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>A99K</t>
+          <t>K143A</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.64126028</v>
+        <v>1.240180744</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>A99R</t>
+          <t>K143K</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>1.008224256</v>
+        <v>0.976943575</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>A99D</t>
+          <t>I144A</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>1.056411444</v>
+        <v>1.312478276</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>A99E</t>
+          <t>I144I</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.819182208</v>
+        <v>1.008457884</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A99N</t>
+          <t>W145A</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>1.141665701</v>
+        <v>1.440389294</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>A99Q</t>
+          <t>W145W</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>1.104598633</v>
+        <v>1.058510022</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>A99S</t>
+          <t>D146A</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.967450481</v>
+        <v>1.212869105</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>A99T</t>
+          <t>D146D</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>0.789528553</v>
+        <v>1.138827677</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>A99C</t>
+          <t>Y147A</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.937796826</v>
+        <v>1.121198766</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>A99G</t>
+          <t>Y147Y</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.859955983</v>
+        <v>0.899074482</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>A99P</t>
+          <t>M148A</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>-0.096374377</v>
+        <v>1.193477303</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>P100A</t>
+          <t>M148M</t>
         </is>
       </c>
       <c r="B287" t="n">
-        <v>1.325147689</v>
+        <v>0.999559277</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>P100P</t>
+          <t>P149A</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>1.061971505</v>
+        <v>0.990744822</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>S101A</t>
+          <t>P149P</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>1.477122669</v>
+        <v>0.923754958</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>S101S</t>
+          <t>T150A</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.980423955</v>
+        <v>1.057734685</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>E102A</t>
+          <t>T150T</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.129734739</v>
+        <v>0.966064346</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>E102E</t>
+          <t>K151A</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.978570601</v>
+        <v>1.262230057</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>H103A</t>
+          <t>K151K</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.698714236</v>
+        <v>0.976641692</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>H103H</t>
+          <t>V152A</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.872929457</v>
+        <v>1.061260467</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>T104A</t>
+          <t>V152V</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>1.212093131</v>
+        <v>0.9131776109999999</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>T104T</t>
+          <t>G153A</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.930383412</v>
+        <v>1.024239753</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>V105A</t>
+          <t>G153G</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.969303834</v>
+        <v>0.985456148</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>V105V</t>
+          <t>Q154A</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.935943473</v>
+        <v>1.066549141</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>N106A</t>
+          <t>Q154Q</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>1.132398934</v>
+        <v>0.992507713</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>N106N</t>
+          <t>E155A</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.9952507819999999</v>
+        <v>0.996033495</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>G107A</t>
+          <t>E155E</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>1.143519055</v>
+        <v>0.893785809</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>G107G</t>
+          <t>N156A</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.9952507819999999</v>
+        <v>1.031291318</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>E108A</t>
+          <t>N156N</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>1.349241283</v>
+        <v>1.147642133</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>E108E</t>
+          <t>L157A</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>1.011930963</v>
+        <v>1.209343323</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Y109A</t>
+          <t>L157L</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>1.11942546</v>
+        <v>0.962538563</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Y109Y</t>
+          <t>L158A</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.985984015</v>
+        <v>1.048920229</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Y110A</t>
+          <t>L158L</t>
         </is>
       </c>
       <c r="B307" t="n">
-        <v>1.345534577</v>
+        <v>1.003085059</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Y110Y</t>
+          <t>L159A</t>
         </is>
       </c>
       <c r="B308" t="n">
-        <v>1.030464497</v>
+        <v>1.285147642</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>P111A</t>
+          <t>L159L</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>1.000810842</v>
+        <v>1.020713971</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>P111P</t>
+          <t>T160A</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.7376346580000001</v>
+        <v>1.200528867</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>F112A</t>
+          <t>T160T</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>1.477122669</v>
+        <v>1.020713971</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>F112F</t>
+          <t>K161A</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>1.017491023</v>
+        <v>1.438519171</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>E113A</t>
+          <t>K161K</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>1.321440982</v>
+        <v>1.156456589</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>E113E</t>
+          <t>V162A</t>
         </is>
       </c>
       <c r="B314" t="n">
-        <v>1.321440982</v>
+        <v>1.181654676</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>A114A</t>
+          <t>V162V</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.364431364</v>
+        <v>1.06294964</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>A114V</t>
+          <t>N163A</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.405494053</v>
+        <v>1.174460432</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>A114I</t>
+          <t>N163N</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.121477121</v>
+        <v>1.073741007</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>A114L</t>
+          <t>P164A</t>
         </is>
       </c>
       <c r="B318" t="n">
-        <v>0.087258214</v>
+        <v>1.043165468</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>A114M</t>
+          <t>P164P</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.381540817</v>
+        <v>0.956834532</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>A114Y</t>
+          <t>Y165A</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.364431364</v>
+        <v>1.008992806</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>A114W</t>
+          <t>L166A</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.309681112</v>
+        <v>1.050359712</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>A114H</t>
+          <t>L166L</t>
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.278884095</v>
+        <v>0.992805755</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>A114K</t>
+          <t>L167A</t>
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.159117919</v>
+        <v>1.025179856</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>A114R</t>
+          <t>L167L</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.203602499</v>
+        <v>0.971223022</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>A114D</t>
+          <t>L168A</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.600541825</v>
+        <v>0.895683453</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>A114E</t>
+          <t>L168L</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.432869178</v>
+        <v>0.910071942</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>A114N</t>
+          <t>P169A</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.802433378</v>
+        <v>0.85971223</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>A114Q</t>
+          <t>P169P</t>
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.935887117</v>
+        <v>0.9244604320000001</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>A114S</t>
+          <t>K170A</t>
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.528682119</v>
+        <v>1.017985612</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>A114T</t>
+          <t>K170K</t>
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.350743801</v>
+        <v>0.899280576</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>A114C</t>
+          <t>K171A</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.237821406</v>
+        <v>1.127697842</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>A114G</t>
+          <t>K171K</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.333634347</v>
+        <v>0.933453237</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>A114P</t>
+          <t>K172A</t>
         </is>
       </c>
       <c r="B333" t="n">
-        <v>0.169383592</v>
+        <v>1.10971223</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>H115A</t>
+          <t>K172K</t>
         </is>
       </c>
       <c r="B334" t="n">
-        <v>0.9170667179999999</v>
+        <v>0.926258993</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>H115H</t>
+          <t>D173A</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>0.889691592</v>
+        <v>1.116906475</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>F116A</t>
+          <t>D173D</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.653581131</v>
+        <v>1.03057554</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>F116F</t>
+          <t>Y174A</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.198469663</v>
+        <v>1.275179856</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>V117A</t>
+          <t>Y174Y</t>
         </is>
       </c>
       <c r="B338" t="n">
-        <v>1.31913888</v>
+        <v>0.922661871</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>V117V</t>
+          <t>Y175A</t>
         </is>
       </c>
       <c r="B339" t="n">
-        <v>1.384154804</v>
+        <v>1.165467626</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>H118A</t>
+          <t>Y175Y</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>-0.219286</v>
+        <v>1.025179856</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>H118H</t>
+          <t>R176A</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>0.864244822</v>
+        <v>1.285971223</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>T119A</t>
+          <t>R176R</t>
         </is>
       </c>
       <c r="B342" t="n">
-        <v>1.267804771</v>
+        <v>1.210431655</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>T119T</t>
+          <t>Y177A</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.785007024</v>
+        <v>0.911870504</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>D120A</t>
+          <t>Y177Y</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>1.317558738</v>
+        <v>1.160071942</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>D120D</t>
+          <t>N178A</t>
         </is>
       </c>
       <c r="B345" t="n">
-        <v>0.027641092</v>
+        <v>1.656208278</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>D121A</t>
+          <t>N178N</t>
         </is>
       </c>
       <c r="B346" t="n">
-        <v>1.468663376</v>
+        <v>1.431909212</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>D121D</t>
+          <t>G179A</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.724196621</v>
+        <v>0.486648865</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>E122A</t>
+          <t>G179G</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.128991765</v>
+        <v>1.075433912</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>E122E</t>
+          <t>S180A</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.972966452</v>
+        <v>1.169559413</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>G123A</t>
+          <t>S180S</t>
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.694712789</v>
+        <v>1.097463284</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>G123G</t>
+          <t>L181A</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>0.698398268</v>
+        <v>0.999332443</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>N124A</t>
+          <t>L181L</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>1.205151628</v>
+        <v>0.939252336</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>N124N</t>
+          <t>T182A</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>1.05404699</v>
+        <v>-0.028037383</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>I125A</t>
+          <t>T182T</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>0.963752755</v>
+        <v>0.97329773</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>I125I</t>
+          <t>T183A</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>1.015349461</v>
+        <v>0.811081442</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>A126A</t>
+          <t>T183T</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>1.12591383</v>
+        <v>0.899198932</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>A126V</t>
+          <t>P184A</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>1.037462335</v>
+        <v>0.108144192</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>A126I</t>
+          <t>P184P</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>1.007978503</v>
+        <v>0.937249666</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>A126L</t>
+          <t>P185A</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.831075511</v>
+        <v>0.88518024</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>A126M</t>
+          <t>P185P</t>
         </is>
       </c>
       <c r="B360" t="n">
-        <v>0.912156049</v>
+        <v>0.897196262</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>A126F</t>
+          <t>C186A</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.952696318</v>
+        <v>-0.038050734</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>A126Y</t>
+          <t>C186C</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.842131948</v>
+        <v>0.831108144</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>A126W</t>
+          <t>S187A</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.757365932</v>
+        <v>0.981308411</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>A126H</t>
+          <t>S187S</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>1.01903494</v>
+        <v>0.905206943</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>A126K</t>
+          <t>E188A</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>1.05588973</v>
+        <v>0.488651535</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>A126R</t>
+          <t>E188E</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>1.218050805</v>
+        <v>0.877169559</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>A126D</t>
+          <t>G189A</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>0.996922066</v>
+        <v>1.091455274</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>A126E</t>
+          <t>G189G</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>1.037462335</v>
+        <v>0.991321762</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>A126N</t>
+          <t>V190A</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.989551108</v>
+        <v>1.021361816</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>A126Q</t>
+          <t>V190V</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.878986738</v>
+        <v>1.14953271</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>A126S</t>
+          <t>R191A</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.960067276</v>
+        <v>1.159546061</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>A126T</t>
+          <t>R191R</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.94532536</v>
+        <v>0.987316422</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>A126C</t>
+          <t>W192A</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.985865629</v>
+        <v>0.398531375</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>A126G</t>
+          <t>W192W</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>1.004293024</v>
+        <v>1.091455274</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>A126P</t>
+          <t>I193A</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.488325966</v>
+        <v>1.297730307</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>V127A</t>
+          <t>I193I</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>1.136970267</v>
+        <v>1.065420561</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>V127V</t>
+          <t>I194A</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.937954402</v>
+        <v>1.276779295</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>I128A</t>
+          <t>I194I</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>1.341514351</v>
+        <v>1.121495327</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>I128I</t>
+          <t>F195A</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>1.035619595</v>
+        <v>1.41480949</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>G129A</t>
+          <t>F195F</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>1.113014654</v>
+        <v>1.11286844</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>G129G</t>
+          <t>K196A</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>1.05404699</v>
+        <v>1.13659238</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>V130A</t>
+          <t>K196K</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>1.421851466</v>
+        <v>1.115025162</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>V130V</t>
+          <t>E197A</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>1.299501796</v>
+        <v>1.01581596</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>L131A</t>
+          <t>E197E</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>1.421851466</v>
+        <v>1.132278936</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>L131L</t>
+          <t>P198A</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>0.954698181</v>
+        <v>1.296189792</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>F132A</t>
+          <t>P198P</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>1.305063144</v>
+        <v>1.153846154</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>F132F</t>
+          <t>V199A</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.874985517</v>
+        <v>1.125808771</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>K133A</t>
+          <t>V199V</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>1.277256401</v>
+        <v>1.086987779</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>K133K</t>
+          <t>E200A</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.97323601</v>
+        <v>1.017972682</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>L134A</t>
+          <t>E200E</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>1.156760514</v>
+        <v>1.134435658</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>L134L</t>
+          <t>I201A</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.956551964</v>
+        <v>1.231488138</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>G135A</t>
+          <t>I201I</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>1.253157224</v>
+        <v>1.080517613</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>G135G</t>
+          <t>S202A</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>1.067778936</v>
+        <v>1.214234364</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>K136A</t>
+          <t>S202S</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>1.106708377</v>
+        <v>1.106398275</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>K136K</t>
+          <t>A203A</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.925037655</v>
+        <v>1.283249461</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>T137A</t>
+          <t>E204A</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>1.077047851</v>
+        <v>1.011502516</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>T137T</t>
+          <t>E204E</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>1.006604101</v>
+        <v>1.041696621</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>N138A</t>
+          <t>Q205A</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>1.101147028</v>
+        <v>1.110711718</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>N138N</t>
+          <t>Q205Q</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>1.101147028</v>
+        <v>1.145219267</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>K139A</t>
+          <t>L206A</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>1.245742092</v>
+        <v>1.3069734</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>K139K</t>
+          <t>L206L</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.978797358</v>
+        <v>1.074047448</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>E140A</t>
+          <t>N207A</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>0.90279226</v>
+        <v>1.339324227</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>E140E</t>
+          <t>N207N</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>1.032557062</v>
+        <v>1.240115025</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>L141A</t>
+          <t>L208A</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>1.021434365</v>
+        <v>1.503235083</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>L141L</t>
+          <t>L208L</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.869424169</v>
+        <v>1.127965492</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Q142A</t>
+          <t>F209A</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>1.208666435</v>
+        <v>1.365204889</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Q142Q</t>
+          <t>F209F</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>1.056656239</v>
+        <v>1.434219986</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>K143A</t>
+          <t>K210A</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>1.240180744</v>
+        <v>1.381349869</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>K143K</t>
+          <t>K210K</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.976943575</v>
+        <v>1.247793942</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>I144A</t>
+          <t>E211A</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>1.312478276</v>
+        <v>1.022656809</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>I144I</t>
+          <t>E211E</t>
         </is>
       </c>
       <c r="B411" t="n">
-        <v>1.008457884</v>
+        <v>0.85475793</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>W145A</t>
+          <t>V212A</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>1.440389294</v>
+        <v>1.211543048</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>W145W</t>
+          <t>V212V</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>1.058510022</v>
+        <v>1.074171238</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>D146A</t>
+          <t>M213A</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>1.212869105</v>
+        <v>0.734557596</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>D146D</t>
+          <t>M213M</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>1.138827677</v>
+        <v>0.662055807</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Y147A</t>
+          <t>G214A</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>1.121198766</v>
+        <v>0.841402337</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Y147Y</t>
+          <t>G214G</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0.899074482</v>
+        <v>0.87574529</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>M148A</t>
+          <t>F215A</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>1.193477303</v>
+        <v>1.028380634</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>M148M</t>
+          <t>F215F</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.999559277</v>
+        <v>0.883377057</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>P149A</t>
+          <t>P216A</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.990744822</v>
+        <v>1.219174815</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>P149P</t>
+          <t>P216P</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>0.923754958</v>
+        <v>0.906272359</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>T150A</t>
+          <t>N217A</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>1.057734685</v>
+        <v>0.152635345</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>T150T</t>
+          <t>N217N</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.966064346</v>
+        <v>1.068447412</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>K151A</t>
+          <t>N218A</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>1.262230057</v>
+        <v>0.988313856</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>K151K</t>
+          <t>N218N</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.976641692</v>
+        <v>1.015025042</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>V152A</t>
+          <t>R219A</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>1.061260467</v>
+        <v>0.053422371</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>V152V</t>
+          <t>R219R</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.9131776109999999</v>
+        <v>1.053183878</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>G153A</t>
+          <t>P220A</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>1.024239753</v>
+        <v>0.746005247</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>G153G</t>
+          <t>P220P</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>0.985456148</v>
+        <v>0.952062962</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Q154A</t>
+          <t>I221A</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>1.066549141</v>
+        <v>0.973050322</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Q154Q</t>
+          <t>I221I</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.992507713</v>
+        <v>0.885284999</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>E155A</t>
+          <t>Q222A</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.996033495</v>
+        <v>1.093250656</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>E155E</t>
+          <t>Q222Q</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.893785809</v>
+        <v>1.036012402</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>N156A</t>
+          <t>P223A</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>1.031291318</v>
+        <v>1.217266873</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>N156N</t>
+          <t>P223P</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>1.147642133</v>
+        <v>1.007393275</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>L157A</t>
+          <t>I224A</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>1.209343323</v>
+        <v>1.387073694</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>L157L</t>
+          <t>I224I</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.962538563</v>
+        <v>0.967326497</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>L158A</t>
+          <t>N225A</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>1.048920229</v>
+        <v>1.518721679</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>L158L</t>
+          <t>N225N</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>1.003085059</v>
+        <v>1.369902218</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>L159A</t>
+          <t>A226A</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>1.285147642</v>
+        <v>1.018267531</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>L159L</t>
+          <t>R227A</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>1.020713971</v>
+        <v>0.217442546</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>T160A</t>
+          <t>R227R</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>1.200528867</v>
+        <v>1.203889216</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>T160T</t>
+          <t>K228A</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>1.020713971</v>
+        <v>1.256923984</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>K161A</t>
+          <t>K228K</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>1.438519171</v>
+        <v>0.942251031</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>K161K</t>
+          <t>I229A</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>1.156456589</v>
+        <v>1.196817914</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>V162A</t>
+          <t>I229I</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>1.181654676</v>
+        <v>1.044784915</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>V162V</t>
+          <t>L230A</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>1.06294964</v>
+        <v>1.092516205</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>N163A</t>
+          <t>L230L</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>1.174460432</v>
+        <v>0.901591043</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>N163N</t>
+          <t>K231A</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>1.073741007</v>
+        <v>0.744254567</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>P164A</t>
+          <t>K231K</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>1.043165468</v>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>P164P</t>
-        </is>
-      </c>
-      <c r="B451" t="n">
-        <v>0.956834532</v>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>Y165A</t>
-        </is>
-      </c>
-      <c r="B452" t="n">
-        <v>1.008992806</v>
-      </c>
-    </row>
-    <row r="453">
-      <c r="A453" t="inlineStr">
-        <is>
-          <t>L166A</t>
-        </is>
-      </c>
-      <c r="B453" t="n">
-        <v>1.050359712</v>
-      </c>
-    </row>
-    <row r="454">
-      <c r="A454" t="inlineStr">
-        <is>
-          <t>L166L</t>
-        </is>
-      </c>
-      <c r="B454" t="n">
-        <v>0.992805755</v>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>L167A</t>
-        </is>
-      </c>
-      <c r="B455" t="n">
-        <v>1.025179856</v>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>L167L</t>
-        </is>
-      </c>
-      <c r="B456" t="n">
-        <v>0.971223022</v>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>L168A</t>
-        </is>
-      </c>
-      <c r="B457" t="n">
-        <v>0.895683453</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>L168L</t>
-        </is>
-      </c>
-      <c r="B458" t="n">
-        <v>0.910071942</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>P169A</t>
-        </is>
-      </c>
-      <c r="B459" t="n">
-        <v>0.85971223</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>P169P</t>
-        </is>
-      </c>
-      <c r="B460" t="n">
-        <v>0.9244604320000001</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>K170A</t>
-        </is>
-      </c>
-      <c r="B461" t="n">
-        <v>1.017985612</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>K170K</t>
-        </is>
-      </c>
-      <c r="B462" t="n">
-        <v>0.899280576</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>K171A</t>
-        </is>
-      </c>
-      <c r="B463" t="n">
-        <v>1.127697842</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>K171K</t>
-        </is>
-      </c>
-      <c r="B464" t="n">
-        <v>0.933453237</v>
-      </c>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr">
-        <is>
-          <t>K172A</t>
-        </is>
-      </c>
-      <c r="B465" t="n">
-        <v>1.10971223</v>
-      </c>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr">
-        <is>
-          <t>K172K</t>
-        </is>
-      </c>
-      <c r="B466" t="n">
-        <v>0.926258993</v>
-      </c>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr">
-        <is>
-          <t>D173A</t>
-        </is>
-      </c>
-      <c r="B467" t="n">
-        <v>1.116906475</v>
-      </c>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr">
-        <is>
-          <t>D173D</t>
-        </is>
-      </c>
-      <c r="B468" t="n">
-        <v>1.03057554</v>
-      </c>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr">
-        <is>
-          <t>Y174A</t>
-        </is>
-      </c>
-      <c r="B469" t="n">
-        <v>1.275179856</v>
-      </c>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr">
-        <is>
-          <t>Y174Y</t>
-        </is>
-      </c>
-      <c r="B470" t="n">
-        <v>0.922661871</v>
-      </c>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr">
-        <is>
-          <t>Y175A</t>
-        </is>
-      </c>
-      <c r="B471" t="n">
-        <v>1.165467626</v>
-      </c>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr">
-        <is>
-          <t>Y175Y</t>
-        </is>
-      </c>
-      <c r="B472" t="n">
-        <v>1.025179856</v>
-      </c>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr">
-        <is>
-          <t>R176A</t>
-        </is>
-      </c>
-      <c r="B473" t="n">
-        <v>1.285971223</v>
-      </c>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr">
-        <is>
-          <t>R176R</t>
-        </is>
-      </c>
-      <c r="B474" t="n">
-        <v>1.210431655</v>
-      </c>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr">
-        <is>
-          <t>Y177A</t>
-        </is>
-      </c>
-      <c r="B475" t="n">
-        <v>0.911870504</v>
-      </c>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr">
-        <is>
-          <t>Y177Y</t>
-        </is>
-      </c>
-      <c r="B476" t="n">
-        <v>1.160071942</v>
-      </c>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr">
-        <is>
-          <t>N178A</t>
-        </is>
-      </c>
-      <c r="B477" t="n">
-        <v>1.656208278</v>
-      </c>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr">
-        <is>
-          <t>N178N</t>
-        </is>
-      </c>
-      <c r="B478" t="n">
-        <v>1.431909212</v>
-      </c>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr">
-        <is>
-          <t>G179A</t>
-        </is>
-      </c>
-      <c r="B479" t="n">
-        <v>0.486648865</v>
-      </c>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr">
-        <is>
-          <t>G179G</t>
-        </is>
-      </c>
-      <c r="B480" t="n">
-        <v>1.075433912</v>
-      </c>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr">
-        <is>
-          <t>S180A</t>
-        </is>
-      </c>
-      <c r="B481" t="n">
-        <v>1.169559413</v>
-      </c>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>S180S</t>
-        </is>
-      </c>
-      <c r="B482" t="n">
-        <v>1.097463284</v>
-      </c>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>L181A</t>
-        </is>
-      </c>
-      <c r="B483" t="n">
-        <v>0.999332443</v>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>L181L</t>
-        </is>
-      </c>
-      <c r="B484" t="n">
-        <v>0.939252336</v>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>T182A</t>
-        </is>
-      </c>
-      <c r="B485" t="n">
-        <v>-0.028037383</v>
-      </c>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>T182T</t>
-        </is>
-      </c>
-      <c r="B486" t="n">
-        <v>0.97329773</v>
-      </c>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>T183A</t>
-        </is>
-      </c>
-      <c r="B487" t="n">
-        <v>0.811081442</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>T183T</t>
-        </is>
-      </c>
-      <c r="B488" t="n">
-        <v>0.899198932</v>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>P184A</t>
-        </is>
-      </c>
-      <c r="B489" t="n">
-        <v>0.108144192</v>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>P184P</t>
-        </is>
-      </c>
-      <c r="B490" t="n">
-        <v>0.937249666</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>P185A</t>
-        </is>
-      </c>
-      <c r="B491" t="n">
-        <v>0.88518024</v>
-      </c>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>P185P</t>
-        </is>
-      </c>
-      <c r="B492" t="n">
-        <v>0.897196262</v>
-      </c>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>C186A</t>
-        </is>
-      </c>
-      <c r="B493" t="n">
-        <v>-0.038050734</v>
-      </c>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>C186C</t>
-        </is>
-      </c>
-      <c r="B494" t="n">
-        <v>0.831108144</v>
-      </c>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>S187A</t>
-        </is>
-      </c>
-      <c r="B495" t="n">
-        <v>0.981308411</v>
-      </c>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>S187S</t>
-        </is>
-      </c>
-      <c r="B496" t="n">
-        <v>0.905206943</v>
-      </c>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>E188A</t>
-        </is>
-      </c>
-      <c r="B497" t="n">
-        <v>0.488651535</v>
-      </c>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>E188E</t>
-        </is>
-      </c>
-      <c r="B498" t="n">
-        <v>0.877169559</v>
-      </c>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>G189A</t>
-        </is>
-      </c>
-      <c r="B499" t="n">
-        <v>1.091455274</v>
-      </c>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>G189G</t>
-        </is>
-      </c>
-      <c r="B500" t="n">
-        <v>0.991321762</v>
-      </c>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>V190A</t>
-        </is>
-      </c>
-      <c r="B501" t="n">
-        <v>1.021361816</v>
-      </c>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>V190V</t>
-        </is>
-      </c>
-      <c r="B502" t="n">
-        <v>1.14953271</v>
-      </c>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>R191A</t>
-        </is>
-      </c>
-      <c r="B503" t="n">
-        <v>1.159546061</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>R191R</t>
-        </is>
-      </c>
-      <c r="B504" t="n">
-        <v>0.987316422</v>
-      </c>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>W192A</t>
-        </is>
-      </c>
-      <c r="B505" t="n">
-        <v>0.398531375</v>
-      </c>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>W192W</t>
-        </is>
-      </c>
-      <c r="B506" t="n">
-        <v>1.091455274</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>I193A</t>
-        </is>
-      </c>
-      <c r="B507" t="n">
-        <v>1.297730307</v>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>I193I</t>
-        </is>
-      </c>
-      <c r="B508" t="n">
-        <v>1.065420561</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>I194A</t>
-        </is>
-      </c>
-      <c r="B509" t="n">
-        <v>1.276779295</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>I194I</t>
-        </is>
-      </c>
-      <c r="B510" t="n">
-        <v>1.121495327</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>F195A</t>
-        </is>
-      </c>
-      <c r="B511" t="n">
-        <v>1.41480949</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>F195F</t>
-        </is>
-      </c>
-      <c r="B512" t="n">
-        <v>1.11286844</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>K196A</t>
-        </is>
-      </c>
-      <c r="B513" t="n">
-        <v>1.13659238</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>K196K</t>
-        </is>
-      </c>
-      <c r="B514" t="n">
-        <v>1.115025162</v>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>E197A</t>
-        </is>
-      </c>
-      <c r="B515" t="n">
-        <v>1.01581596</v>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>E197E</t>
-        </is>
-      </c>
-      <c r="B516" t="n">
-        <v>1.132278936</v>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>P198A</t>
-        </is>
-      </c>
-      <c r="B517" t="n">
-        <v>1.296189792</v>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>P198P</t>
-        </is>
-      </c>
-      <c r="B518" t="n">
-        <v>1.153846154</v>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>V199A</t>
-        </is>
-      </c>
-      <c r="B519" t="n">
-        <v>1.125808771</v>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>V199V</t>
-        </is>
-      </c>
-      <c r="B520" t="n">
-        <v>1.086987779</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>E200A</t>
-        </is>
-      </c>
-      <c r="B521" t="n">
-        <v>1.017972682</v>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>E200E</t>
-        </is>
-      </c>
-      <c r="B522" t="n">
-        <v>1.134435658</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>I201A</t>
-        </is>
-      </c>
-      <c r="B523" t="n">
-        <v>1.231488138</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>I201I</t>
-        </is>
-      </c>
-      <c r="B524" t="n">
-        <v>1.080517613</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>S202A</t>
-        </is>
-      </c>
-      <c r="B525" t="n">
-        <v>1.214234364</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>S202S</t>
-        </is>
-      </c>
-      <c r="B526" t="n">
-        <v>1.106398275</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>A203A</t>
-        </is>
-      </c>
-      <c r="B527" t="n">
-        <v>1.283249461</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>A203V</t>
-        </is>
-      </c>
-      <c r="B528" t="n">
-        <v>1.205607477</v>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>A203I</t>
-        </is>
-      </c>
-      <c r="B529" t="n">
-        <v>0.968368081</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>A203L</t>
-        </is>
-      </c>
-      <c r="B530" t="n">
-        <v>1.434219986</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>A203M</t>
-        </is>
-      </c>
-      <c r="B531" t="n">
-        <v>1.127965492</v>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>A203F</t>
-        </is>
-      </c>
-      <c r="B532" t="n">
-        <v>0.920920201</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>A203Y</t>
-        </is>
-      </c>
-      <c r="B533" t="n">
-        <v>0.998562185</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>A203W</t>
-        </is>
-      </c>
-      <c r="B534" t="n">
-        <v>1.067577283</v>
-      </c>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr">
-        <is>
-          <t>A203H</t>
-        </is>
-      </c>
-      <c r="B535" t="n">
-        <v>0.968368081</v>
-      </c>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr">
-        <is>
-          <t>A203K</t>
-        </is>
-      </c>
-      <c r="B536" t="n">
-        <v>0.972681524</v>
-      </c>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr">
-        <is>
-          <t>A203R</t>
-        </is>
-      </c>
-      <c r="B537" t="n">
-        <v>0.89503954</v>
-      </c>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr">
-        <is>
-          <t>A203D</t>
-        </is>
-      </c>
-      <c r="B538" t="n">
-        <v>1.27030913</v>
-      </c>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr">
-        <is>
-          <t>A203E</t>
-        </is>
-      </c>
-      <c r="B539" t="n">
-        <v>1.397555715</v>
-      </c>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr">
-        <is>
-          <t>A203N</t>
-        </is>
-      </c>
-      <c r="B540" t="n">
-        <v>1.287562904</v>
-      </c>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr">
-        <is>
-          <t>A203Q</t>
-        </is>
-      </c>
-      <c r="B541" t="n">
-        <v>1.115025162</v>
-      </c>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr">
-        <is>
-          <t>A203S</t>
-        </is>
-      </c>
-      <c r="B542" t="n">
-        <v>1.115025162</v>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>A203T</t>
-        </is>
-      </c>
-      <c r="B543" t="n">
-        <v>1.261682243</v>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>A203C</t>
-        </is>
-      </c>
-      <c r="B544" t="n">
-        <v>0.938173976</v>
-      </c>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr">
-        <is>
-          <t>A203G</t>
-        </is>
-      </c>
-      <c r="B545" t="n">
-        <v>0.964054637</v>
-      </c>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr">
-        <is>
-          <t>A203P</t>
-        </is>
-      </c>
-      <c r="B546" t="n">
-        <v>1.115025162</v>
-      </c>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr">
-        <is>
-          <t>E204A</t>
-        </is>
-      </c>
-      <c r="B547" t="n">
-        <v>1.011502516</v>
-      </c>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr">
-        <is>
-          <t>E204E</t>
-        </is>
-      </c>
-      <c r="B548" t="n">
-        <v>1.041696621</v>
-      </c>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr">
-        <is>
-          <t>Q205A</t>
-        </is>
-      </c>
-      <c r="B549" t="n">
-        <v>1.110711718</v>
-      </c>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr">
-        <is>
-          <t>Q205Q</t>
-        </is>
-      </c>
-      <c r="B550" t="n">
-        <v>1.145219267</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr">
-        <is>
-          <t>L206A</t>
-        </is>
-      </c>
-      <c r="B551" t="n">
-        <v>1.3069734</v>
-      </c>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr">
-        <is>
-          <t>L206L</t>
-        </is>
-      </c>
-      <c r="B552" t="n">
-        <v>1.074047448</v>
-      </c>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr">
-        <is>
-          <t>N207A</t>
-        </is>
-      </c>
-      <c r="B553" t="n">
-        <v>1.339324227</v>
-      </c>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr">
-        <is>
-          <t>N207N</t>
-        </is>
-      </c>
-      <c r="B554" t="n">
-        <v>1.240115025</v>
-      </c>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr">
-        <is>
-          <t>L208A</t>
-        </is>
-      </c>
-      <c r="B555" t="n">
-        <v>1.503235083</v>
-      </c>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr">
-        <is>
-          <t>L208L</t>
-        </is>
-      </c>
-      <c r="B556" t="n">
-        <v>1.127965492</v>
-      </c>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr">
-        <is>
-          <t>F209A</t>
-        </is>
-      </c>
-      <c r="B557" t="n">
-        <v>1.365204889</v>
-      </c>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr">
-        <is>
-          <t>F209F</t>
-        </is>
-      </c>
-      <c r="B558" t="n">
-        <v>1.434219986</v>
-      </c>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr">
-        <is>
-          <t>K210A</t>
-        </is>
-      </c>
-      <c r="B559" t="n">
-        <v>1.381349869</v>
-      </c>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr">
-        <is>
-          <t>K210K</t>
-        </is>
-      </c>
-      <c r="B560" t="n">
-        <v>1.247793942</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr">
-        <is>
-          <t>E211A</t>
-        </is>
-      </c>
-      <c r="B561" t="n">
-        <v>1.022656809</v>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr">
-        <is>
-          <t>E211E</t>
-        </is>
-      </c>
-      <c r="B562" t="n">
-        <v>0.85475793</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr">
-        <is>
-          <t>V212A</t>
-        </is>
-      </c>
-      <c r="B563" t="n">
-        <v>1.211543048</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr">
-        <is>
-          <t>V212V</t>
-        </is>
-      </c>
-      <c r="B564" t="n">
-        <v>1.074171238</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr">
-        <is>
-          <t>M213A</t>
-        </is>
-      </c>
-      <c r="B565" t="n">
-        <v>0.734557596</v>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr">
-        <is>
-          <t>M213M</t>
-        </is>
-      </c>
-      <c r="B566" t="n">
-        <v>0.662055807</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr">
-        <is>
-          <t>G214A</t>
-        </is>
-      </c>
-      <c r="B567" t="n">
-        <v>0.841402337</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr">
-        <is>
-          <t>G214G</t>
-        </is>
-      </c>
-      <c r="B568" t="n">
-        <v>0.87574529</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr">
-        <is>
-          <t>F215A</t>
-        </is>
-      </c>
-      <c r="B569" t="n">
-        <v>1.028380634</v>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr">
-        <is>
-          <t>F215F</t>
-        </is>
-      </c>
-      <c r="B570" t="n">
-        <v>0.883377057</v>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr">
-        <is>
-          <t>P216A</t>
-        </is>
-      </c>
-      <c r="B571" t="n">
-        <v>1.219174815</v>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr">
-        <is>
-          <t>P216P</t>
-        </is>
-      </c>
-      <c r="B572" t="n">
-        <v>0.906272359</v>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>N217A</t>
-        </is>
-      </c>
-      <c r="B573" t="n">
-        <v>0.152635345</v>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>N217N</t>
-        </is>
-      </c>
-      <c r="B574" t="n">
-        <v>1.068447412</v>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>N218A</t>
-        </is>
-      </c>
-      <c r="B575" t="n">
-        <v>0.988313856</v>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>N218N</t>
-        </is>
-      </c>
-      <c r="B576" t="n">
-        <v>1.015025042</v>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>R219A</t>
-        </is>
-      </c>
-      <c r="B577" t="n">
-        <v>0.053422371</v>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>R219R</t>
-        </is>
-      </c>
-      <c r="B578" t="n">
-        <v>1.053183878</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>P220A</t>
-        </is>
-      </c>
-      <c r="B579" t="n">
-        <v>0.746005247</v>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>P220P</t>
-        </is>
-      </c>
-      <c r="B580" t="n">
-        <v>0.952062962</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>I221A</t>
-        </is>
-      </c>
-      <c r="B581" t="n">
-        <v>0.973050322</v>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>I221I</t>
-        </is>
-      </c>
-      <c r="B582" t="n">
-        <v>0.885284999</v>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>Q222A</t>
-        </is>
-      </c>
-      <c r="B583" t="n">
-        <v>1.093250656</v>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>Q222Q</t>
-        </is>
-      </c>
-      <c r="B584" t="n">
-        <v>1.036012402</v>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>P223A</t>
-        </is>
-      </c>
-      <c r="B585" t="n">
-        <v>1.217266873</v>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>P223P</t>
-        </is>
-      </c>
-      <c r="B586" t="n">
-        <v>1.007393275</v>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>I224A</t>
-        </is>
-      </c>
-      <c r="B587" t="n">
-        <v>1.387073694</v>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>I224I</t>
-        </is>
-      </c>
-      <c r="B588" t="n">
-        <v>0.967326497</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>N225A</t>
-        </is>
-      </c>
-      <c r="B589" t="n">
-        <v>1.518721679</v>
-      </c>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>N225N</t>
-        </is>
-      </c>
-      <c r="B590" t="n">
-        <v>1.369902218</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>A226A</t>
-        </is>
-      </c>
-      <c r="B591" t="n">
-        <v>1.018267531</v>
-      </c>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>A226V</t>
-        </is>
-      </c>
-      <c r="B592" t="n">
-        <v>1.520329994</v>
-      </c>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>A226I</t>
-        </is>
-      </c>
-      <c r="B593" t="n">
-        <v>0.8379493220000001</v>
-      </c>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>A226L</t>
-        </is>
-      </c>
-      <c r="B594" t="n">
-        <v>0.855627578</v>
-      </c>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>A226M</t>
-        </is>
-      </c>
-      <c r="B595" t="n">
-        <v>1.442545669</v>
-      </c>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>A226F</t>
-        </is>
-      </c>
-      <c r="B596" t="n">
-        <v>1.32233353</v>
-      </c>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>A226Y</t>
-        </is>
-      </c>
-      <c r="B597" t="n">
-        <v>1.184443135</v>
-      </c>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>A226W</t>
-        </is>
-      </c>
-      <c r="B598" t="n">
-        <v>1.223335298</v>
-      </c>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>A226H</t>
-        </is>
-      </c>
-      <c r="B599" t="n">
-        <v>1.378903948</v>
-      </c>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>A226K</t>
-        </is>
-      </c>
-      <c r="B600" t="n">
-        <v>1.071302298</v>
-      </c>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>A226R</t>
-        </is>
-      </c>
-      <c r="B601" t="n">
-        <v>1.110194461</v>
-      </c>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>A226D</t>
-        </is>
-      </c>
-      <c r="B602" t="n">
-        <v>1.534472599</v>
-      </c>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>A226E</t>
-        </is>
-      </c>
-      <c r="B603" t="n">
-        <v>1.460223925</v>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>A226N</t>
-        </is>
-      </c>
-      <c r="B604" t="n">
-        <v>1.594578668</v>
-      </c>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>A226Q</t>
-        </is>
-      </c>
-      <c r="B605" t="n">
-        <v>1.587507366</v>
-      </c>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>A226S</t>
-        </is>
-      </c>
-      <c r="B606" t="n">
-        <v>1.120801414</v>
-      </c>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>A226T</t>
-        </is>
-      </c>
-      <c r="B607" t="n">
-        <v>1.177371833</v>
-      </c>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>A226C</t>
-        </is>
-      </c>
-      <c r="B608" t="n">
-        <v>1.2304066</v>
-      </c>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>A226G</t>
-        </is>
-      </c>
-      <c r="B609" t="n">
-        <v>1.467295227</v>
-      </c>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>A226P</t>
-        </is>
-      </c>
-      <c r="B610" t="n">
-        <v>0.869770183</v>
-      </c>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>R227A</t>
-        </is>
-      </c>
-      <c r="B611" t="n">
-        <v>0.217442546</v>
-      </c>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>R227R</t>
-        </is>
-      </c>
-      <c r="B612" t="n">
-        <v>1.203889216</v>
-      </c>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>K228A</t>
-        </is>
-      </c>
-      <c r="B613" t="n">
-        <v>1.256923984</v>
-      </c>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>K228K</t>
-        </is>
-      </c>
-      <c r="B614" t="n">
-        <v>0.942251031</v>
-      </c>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>I229A</t>
-        </is>
-      </c>
-      <c r="B615" t="n">
-        <v>1.196817914</v>
-      </c>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>I229I</t>
-        </is>
-      </c>
-      <c r="B616" t="n">
-        <v>1.044784915</v>
-      </c>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>L230A</t>
-        </is>
-      </c>
-      <c r="B617" t="n">
-        <v>1.092516205</v>
-      </c>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>L230L</t>
-        </is>
-      </c>
-      <c r="B618" t="n">
-        <v>0.901591043</v>
-      </c>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>K231A</t>
-        </is>
-      </c>
-      <c r="B619" t="n">
-        <v>0.744254567</v>
-      </c>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>K231K</t>
-        </is>
-      </c>
-      <c r="B620" t="n">
         <v>0.889216264</v>
       </c>
     </row>
